--- a/artfynd/A 4956-2020 artfynd.xlsx
+++ b/artfynd/A 4956-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4956-2020 artfynd.xlsx
+++ b/artfynd/A 4956-2020 artfynd.xlsx
@@ -1696,7 +1696,7 @@
         <v>86418865</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408636.7948584739</v>
+        <v>408637</v>
       </c>
       <c r="R11" t="n">
-        <v>6751367.015126976</v>
+        <v>6751367</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,19 +1766,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 4956-2020 artfynd.xlsx
+++ b/artfynd/A 4956-2020 artfynd.xlsx
@@ -1696,7 +1696,7 @@
         <v>86418865</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
